--- a/dev/review_manual/Excel_stars_OR.xlsx
+++ b/dev/review_manual/Excel_stars_OR.xlsx
@@ -6,14 +6,14 @@
     <workbookView activeTab="0" firstSheet="0" windowHeight="13125" windowWidth="13125" xWindow="0" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="levels by Pop, rock  OR (" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="logit_married_race_rincom" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="12">
+  <numFmts count="8">
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="@"/>
@@ -22,12 +22,8 @@
     <numFmt numFmtId="170" formatCode="@"/>
     <numFmt numFmtId="171" formatCode="@"/>
     <numFmt numFmtId="172" formatCode="@"/>
-    <numFmt numFmtId="173" formatCode="@"/>
-    <numFmt numFmtId="174" formatCode="@"/>
-    <numFmt numFmtId="175" formatCode="@"/>
-    <numFmt numFmtId="176" formatCode="@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -38,64 +34,42 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="DejaVu Sans"/>
+      <name val="Cascadia Mono"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
       <color rgb="FF0267C7"/>
-      <name val="DejaVu Sans"/>
+      <name val="Cascadia Mono"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
       <color rgb="FF02A5B3"/>
-      <name val="DejaVu Sans"/>
+      <name val="Cascadia Mono"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-      <color rgb="FF0891C9"/>
-      <name val="DejaVu Sans"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-      <color rgb="FFD60103"/>
-      <name val="DejaVu Sans"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
       <color rgb="FFDD5301"/>
-      <name val="DejaVu Sans"/>
+      <name val="Cascadia Mono"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="DejaVu Sans"/>
+      <name val="Cascadia Mono"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="DejaVu Sans Condensed"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -103,14 +77,12 @@
       <color rgb="FF000000"/>
       <name val="DejaVu Sans Condensed"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="DejaVu Sans Condensed"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -118,7 +90,6 @@
       <color rgb="FF000000"/>
       <name val="DejaVu Sans Condensed"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -126,7 +97,6 @@
       <color rgb="FF000000"/>
       <name val="DejaVu Sans Condensed"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,15 +122,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -171,7 +133,15 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="double">
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -220,7 +190,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -228,7 +198,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -244,109 +214,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fontId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="3" fontId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="4" fontId="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="2">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="3" fontId="2">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="3">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="4">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fontId="3">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fontId="4">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fontId="5">
       <alignment vertical="top"/>
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="3" fontId="5">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="6">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="7">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="3" fontId="7">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyFont="1" fontId="8">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fontId="5">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="4" fontId="5">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" fontId="6">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="5" fontId="9">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="5" fontId="7">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="6" fontId="9">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="6" fontId="7">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="7" fontId="10">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="8" fontId="10">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="9" fontId="10">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="10" fontId="10">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="7" fontId="11">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="9" fontId="11">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyFont="1" fontId="12"/>
-    <xf applyAlignment="1" applyFont="1" fontId="9">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="7" fontId="8">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="8" fontId="8">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="7" fontId="9">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="9" fontId="9">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="8" fontId="9">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="10" fontId="9">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyFont="1" fontId="10"/>
+    <xf applyAlignment="1" applyFont="1" fontId="7">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="3" fontId="7" numFmtId="165">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="7" numFmtId="166">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="4" numFmtId="167">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="2" numFmtId="168">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="3" fontId="2" numFmtId="169">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="1" numFmtId="170">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="3" numFmtId="171">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="6" numFmtId="172">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="3" fontId="5" numFmtId="173">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="3" fontId="1" numFmtId="174">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="4" fontId="1" numFmtId="175">
-      <alignment vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fontId="1" numFmtId="176">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="5" numFmtId="165">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fontId="5" numFmtId="166">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fontId="4" numFmtId="167">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="1" numFmtId="168">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fontId="3" numFmtId="169">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fontId="2" numFmtId="170">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="4" fontId="5" numFmtId="171">
+      <alignment vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="3" fontId="5" numFmtId="172">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -674,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
@@ -682,510 +628,372 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>levels by Pop, rock: OR (tabbed by var)</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Logistic regression: married by race, rincome</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>Pop, rock: OR</t>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>married: 01-Married</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>levels</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Pop, rock: OR</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Model OR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Reference population</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>1/2.43***</t>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>1/1.51***</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Brevet ou -</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">1   </t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>CAP BEP</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>1.93***</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>1/2.33***</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Bac pro</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>2.40***</t>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/1.04   </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Bac</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>2.87***</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>1-Lt $10000</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1   </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Bac+2</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>3.27***</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2-$10000 to 14999</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>1.21***</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Licence</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>3.44***</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>3-$15000 to 24999</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>1.33***</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Bac+5</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>3.17***</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>4-$25000 or more</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>2.07***</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>&lt; 1200€</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1   </t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>13 015</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>1200_2499€</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.18   </t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>LR vs null</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>2500_3999€</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>1.42***</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>McFadden R2</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>0.031</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>4000_5999€</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>1.64***</t>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>17 483</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>6000€+</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>2.07***</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>17 528</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>15 à 29 ans</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1   </t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>Model: logistic regression; odds ratios (vs the reference category).</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>30 à 44 ans</t>
-        </is>
-      </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/1.02   </t>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">Shades of blue: OR ≥ </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FF02A5B3"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1.2</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FF0891C9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1.5</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FF0267C7"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FF300DFD"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve"> </t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">Shades of yellow to red: OR ≤ </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FFDCA331"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1/1.2</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FFDE7C01"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1/1.5</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FFDD5301"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1/2</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="9"/>
+              <color rgb="FFD60103"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>1/4</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t xml:space="preserve"> Coloured: significantly different from the reference category (Wald interval on the log odds-ratio, 95% confidence), by at least the first colour threshold. Uncoloured: either not significant, or a difference under ×1.2.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>45 à 59 ans</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/1.31** </t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>60 à 74 ans</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>1/3.20***</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>75 ans ou plus</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>1/17.27***</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Agriculteurs, artisans, etc.</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1   </t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Cadres et professions supérieures</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>1.63***</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Professions intermédiaires</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.45** </t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Employées</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/1.08   </t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Ouvriers</t>
-        </is>
-      </c>
-      <c r="B26" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.24   </t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Jamais travaillé</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/1.36   </t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 459   </t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Wald vs null</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;0.01%   </t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Nagelkerke R2</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.231   </t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 985   </t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">Shades of blue: OR ≥ </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FF02A5B3"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>1.15</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FF0891C9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>1.5</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FF0267C7"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FF300DFD"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>4</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>.</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve"> </t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">Shades of yellow to red: OR ≤ </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FFDCA331"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>1/1.5</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FFDD5301"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>1/2</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b/>
-              <sz val="9"/>
-              <color rgb="FFD60103"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>1/4</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t>.</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="9"/>
-              <rFont val="DejaVu Sans Condensed"/>
-            </rPr>
-            <t xml:space="preserve"> Grey: not significantly different from the reference category (Wald interval on the log odds-ratio, 95% confidence).</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="DejaVu Sans Condensed"/>
+            </rPr>
+            <t>***: significantly different from the reference category (in bold) at the 99% confidence level; **: at the 95% level; *: at the 90% level; no star: not significant.</t>
           </r>
         </is>
       </c>

--- a/dev/review_manual/Excel_stars_OR.xlsx
+++ b/dev/review_manual/Excel_stars_OR.xlsx
@@ -638,7 +638,7 @@
       <c r="A2" s="19"/>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>married: 01-Married</t>
+          <t>married: Married</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Model OR</t>
+          <t>Model_OR</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>1-Lt $10000</t>
+          <t>Lt $10000</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2-$10000 to 14999</t>
+          <t>$10000 to 14999</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>3-$15000 to 24999</t>
+          <t>$15000 to 24999</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>4-$25000 or more</t>
+          <t>$25000 or more</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
